--- a/input/bigramas_rev.xlsx
+++ b/input/bigramas_rev.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/soledadaraya/Library/CloudStorage/Dropbox/Lucía Miranda Fondecyt/femocratas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/soledadaraya/Library/CloudStorage/Dropbox/Lucía Miranda Fondecyt/femocratas/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BE70CB2-BD1D-B649-A1DD-9F3FCF557984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE3D682-F945-F846-8E47-A329CCB5DF12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="15120" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1275,6 +1275,9 @@
       <c r="C5">
         <v>6</v>
       </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -1308,6 +1311,9 @@
       <c r="C8">
         <v>6</v>
       </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -1319,6 +1325,9 @@
       <c r="C9">
         <v>6</v>
       </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -1330,6 +1339,9 @@
       <c r="C10">
         <v>6</v>
       </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -1352,6 +1364,9 @@
       <c r="C12">
         <v>6</v>
       </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -1637,6 +1652,9 @@
       <c r="C36">
         <v>6</v>
       </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
@@ -2074,9 +2092,6 @@
       <c r="C73">
         <v>7</v>
       </c>
-      <c r="D73">
-        <v>1</v>
-      </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
@@ -2376,6 +2391,9 @@
       <c r="C98">
         <v>7</v>
       </c>
+      <c r="D98">
+        <v>1</v>
+      </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
@@ -2484,6 +2502,9 @@
       <c r="C107">
         <v>8</v>
       </c>
+      <c r="D107">
+        <v>1</v>
+      </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
@@ -2553,6 +2574,9 @@
       <c r="C113">
         <v>8</v>
       </c>
+      <c r="D113">
+        <v>1</v>
+      </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
@@ -2600,6 +2624,9 @@
       <c r="C117">
         <v>8</v>
       </c>
+      <c r="D117">
+        <v>1</v>
+      </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
@@ -3106,9 +3133,6 @@
       <c r="C160">
         <v>9</v>
       </c>
-      <c r="D160">
-        <v>1</v>
-      </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
@@ -3913,6 +3937,9 @@
       </c>
       <c r="C225">
         <v>16</v>
+      </c>
+      <c r="D225">
+        <v>1</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.2">
